--- a/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260622.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260622.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D71"/>
+  <dimension ref="A1:D72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -611,12 +611,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>35,853</t>
+          <t>35,491</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>10.92%</t>
+          <t>10.81%</t>
         </is>
       </c>
     </row>
@@ -633,12 +633,12 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>86,630</t>
+          <t>85,789</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>10.03%</t>
+          <t>10.10%</t>
         </is>
       </c>
     </row>
@@ -655,12 +655,12 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>99,979</t>
+          <t>98,956</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>9.14%</t>
+          <t>9.57%</t>
         </is>
       </c>
     </row>
@@ -677,56 +677,56 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>39,388</t>
+          <t>38,952</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>7.59%</t>
+          <t>7.79%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>NEE US</t>
+          <t>BE UN</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Nextera Energy Inc</t>
+          <t>Bloom Energy Corp</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>215,990</t>
+          <t>53,677</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.14%</t>
+          <t>5.02%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>BE UN</t>
+          <t>NEE US</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Bloom Energy Corp</t>
+          <t>Nextera Energy Inc</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>54,228</t>
+          <t>213,803</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.90%</t>
+          <t>4.97%</t>
         </is>
       </c>
     </row>
@@ -743,56 +743,56 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>114,848</t>
+          <t>113,709</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.90%</t>
+          <t>3.79%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>SO US</t>
+          <t>NVT US</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>南方公司</t>
+          <t>nVent Electric PLC</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>124,568</t>
+          <t>64,593</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.18%</t>
+          <t>3.22%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>NVT US</t>
+          <t>SO US</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>nVent Electric PLC</t>
+          <t>南方公司</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>65,278</t>
+          <t>123,322</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.17%</t>
+          <t>3.11%</t>
         </is>
       </c>
     </row>
@@ -809,7 +809,7 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>21,486</t>
+          <t>21,231</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -831,12 +831,12 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>129,522</t>
+          <t>128,270</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.43%</t>
+          <t>2.36%</t>
         </is>
       </c>
     </row>
@@ -853,56 +853,56 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>59,983</t>
+          <t>59,409</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.10%</t>
+          <t>2.09%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>EXC US</t>
+          <t>FSLR US</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Exelon Corp</t>
+          <t>第一太陽能</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>150,828</t>
+          <t>26,626</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>1.90%</t>
+          <t>1.89%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>FSLR US</t>
+          <t>EXC US</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>第一太陽能</t>
+          <t>Exelon Corp</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>26,897</t>
+          <t>149,324</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>1.90%</t>
+          <t>1.85%</t>
         </is>
       </c>
     </row>
@@ -919,12 +919,12 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>24,914</t>
+          <t>24,684</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.87%</t>
+          <t>1.84%</t>
         </is>
       </c>
     </row>
@@ -941,12 +941,12 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>68,920</t>
+          <t>68,256</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.46%</t>
+          <t>1.45%</t>
         </is>
       </c>
     </row>
@@ -963,12 +963,12 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>12,587</t>
+          <t>12,420</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.31%</t>
+          <t>1.36%</t>
         </is>
       </c>
     </row>
@@ -985,12 +985,12 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>55,058</t>
+          <t>54,489</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.21%</t>
+          <t>1.19%</t>
         </is>
       </c>
     </row>
@@ -1007,34 +1007,34 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>40,658</t>
+          <t>40,294</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.19%</t>
+          <t>1.16%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>EIX US</t>
+          <t>AGX US</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>愛迪生國際</t>
+          <t>阿根公司</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>56,706</t>
+          <t>5,391</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.12%</t>
+          <t>1.15%</t>
         </is>
       </c>
     </row>
@@ -1051,56 +1051,56 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>24,608</t>
+          <t>24,385</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.11%</t>
+          <t>1.10%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>WEC US</t>
+          <t>EIX US</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>WEC能源集團公司</t>
+          <t>愛迪生國際</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>35,981</t>
+          <t>56,103</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.11%</t>
+          <t>1.09%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>AGX US</t>
+          <t>WEC US</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>阿根公司</t>
+          <t>WEC能源集團公司</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>5,407</t>
+          <t>35,617</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.10%</t>
+          <t>1.09%</t>
         </is>
       </c>
     </row>
@@ -1117,12 +1117,12 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>85,169</t>
+          <t>84,359</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.09%</t>
+          <t>1.07%</t>
         </is>
       </c>
     </row>
@@ -1139,29 +1139,29 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>55,420</t>
+          <t>54,843</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.06%</t>
+          <t>1.04%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>ETR US</t>
+          <t>AEIS US</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>安特吉公司</t>
+          <t>艾儀有限公司</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>33,669</t>
+          <t>9,865</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -1173,22 +1173,22 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>AEIS US</t>
+          <t>ETR US</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>艾儀有限公司</t>
+          <t>安特吉公司</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>9,976</t>
+          <t>33,354</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.02%</t>
+          <t>1.01%</t>
         </is>
       </c>
     </row>
@@ -1205,29 +1205,29 @@
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>52,026</t>
+          <t>51,521</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.98%</t>
+          <t>0.94%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>DTE US</t>
+          <t>GNRC US</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>DTE能源</t>
+          <t>基內瑞克控股公司</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>22,874</t>
+          <t>11,663</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -1249,34 +1249,34 @@
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>14,630</t>
+          <t>14,519</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.92%</t>
+          <t>0.91%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>GNRC US</t>
+          <t>DTE US</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>基內瑞克控股公司</t>
+          <t>DTE能源</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>11,814</t>
+          <t>22,688</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.91%</t>
+          <t>0.90%</t>
         </is>
       </c>
     </row>
@@ -1293,12 +1293,12 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>30,551</t>
+          <t>30,203</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.91%</t>
+          <t>0.90%</t>
         </is>
       </c>
     </row>
@@ -1315,12 +1315,12 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>83,112</t>
+          <t>82,248</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>0.81%</t>
+          <t>0.79%</t>
         </is>
       </c>
     </row>
@@ -1337,12 +1337,12 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>105,181</t>
+          <t>104,147</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.79%</t>
+          <t>0.76%</t>
         </is>
       </c>
     </row>
@@ -1359,12 +1359,12 @@
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>33,523</t>
+          <t>33,211</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.76%</t>
+          <t>0.75%</t>
         </is>
       </c>
     </row>
@@ -1381,12 +1381,12 @@
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>161,521</t>
+          <t>159,890</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.73%</t>
+          <t>0.72%</t>
         </is>
       </c>
     </row>
@@ -1403,34 +1403,34 @@
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>33,945</t>
+          <t>33,623</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>0.68%</t>
+          <t>0.67%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>202609ESU6</t>
+          <t>VICR US</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>小型S＆P 500股價指數</t>
+          <t>懷克爾公司</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6,439</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>0.62%</t>
+          <t>0.64%</t>
         </is>
       </c>
     </row>
@@ -1447,7 +1447,7 @@
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>7,540</t>
+          <t>7,479</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -1459,83 +1459,83 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>VICR US</t>
+          <t>202609ESU6</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>懷克爾公司</t>
+          <t>小型S＆P 500股價指數</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>6,477</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>0.59%</t>
+          <t>0.61%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>CNP US</t>
+          <t>LNT US</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>Centerpoint能源</t>
+          <t>聯合能源公司</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>48,160</t>
+          <t>28,244</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>0.57%</t>
+          <t>0.56%</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>LNT US</t>
+          <t>NRG US</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>聯合能源公司</t>
+          <t>NRG Energy Inc</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>28,550</t>
+          <t>14,706</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>0.57%</t>
+          <t>0.55%</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>NRG US</t>
+          <t>CNP US</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>NRG Energy Inc</t>
+          <t>Centerpoint能源</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>14,822</t>
+          <t>47,638</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>4,086</t>
+          <t>4,000</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>17,847</t>
+          <t>17,668</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>0.50%</t>
+          <t>0.49%</t>
         </is>
       </c>
     </row>
@@ -1601,12 +1601,12 @@
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>104,553</t>
+          <t>103,531</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>0.42%</t>
+          <t>0.41%</t>
         </is>
       </c>
     </row>
@@ -1623,12 +1623,12 @@
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>26,019</t>
+          <t>25,766</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>0.37%</t>
+          <t>0.36%</t>
         </is>
       </c>
     </row>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>3,177</t>
+          <t>3,110</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
@@ -1667,12 +1667,12 @@
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>8,876</t>
+          <t>8,788</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>0.20%</t>
+          <t>0.19%</t>
         </is>
       </c>
     </row>
@@ -1689,7 +1689,7 @@
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>20,449</t>
+          <t>20,216</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -1711,14 +1711,28 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>42,316</t>
+          <t>41,917</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>0.02%</t>
-        </is>
-      </c>
+          <t>0.01%</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>C_NTD</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr"/>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>135,501,017</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="5">
